--- a/artfynd/A 49036-2021 artfynd.xlsx
+++ b/artfynd/A 49036-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49036-2021 artfynd.xlsx
+++ b/artfynd/A 49036-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64172948</v>
+        <v>75235036</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallåsens nordöstra del, Hls</t>
+          <t>Vallåsens nordostsida, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595356.213586546</v>
+        <v>595425</v>
       </c>
       <c r="R2" t="n">
-        <v>6846461.22412124</v>
+        <v>6846164</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-02-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-02-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ca 100-årig naturskogsartad granskog</t>
+          <t>grannaturskog i nordsluttning</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter # torrgran, granstubbe</t>
+          <t>5 substratenheter # gamla senvuxna granar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,12 +788,7 @@
         <v>75235037</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595281.9653023257</v>
+        <v>595282</v>
       </c>
       <c r="R3" t="n">
-        <v>6846074.2153187</v>
+        <v>6846074</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,19 +853,9 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-05-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75235051</v>
+        <v>75235038</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595207.7750093609</v>
+        <v>595304</v>
       </c>
       <c r="R4" t="n">
-        <v>6846284.074679539</v>
+        <v>6846307</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,21 +963,11 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1024,15 +979,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>äldre oskött granskog med björkinslag</t>
+          <t>ljus kant mellan grannaturskog och tallskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # grövre granlåga</t>
+          <t>5 substratenheter # senvuxen gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,37 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75235076</v>
+        <v>75235069</v>
       </c>
       <c r="B5" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595226.8652285029</v>
+        <v>595132</v>
       </c>
       <c r="R5" t="n">
-        <v>6846366.143165261</v>
+        <v>6846434</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,21 +1073,11 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1149,15 +1089,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>naturskogsartad granskog i nordsluttning</t>
+          <t>olikåldrig barrskog i nordsluttning</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10 substratenheter # äldre granar</t>
+          <t>1 substratenheter # grov tallhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1175,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75235053</v>
+        <v>75235049</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595214.8062696656</v>
+        <v>595296</v>
       </c>
       <c r="R6" t="n">
-        <v>6846355.853592806</v>
+        <v>6846103</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,21 +1183,11 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1274,15 +1199,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>naturskogsartad olikåldrig granskog i nordsluttning</t>
+          <t>naturskogsartad luckig granskog</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlågor</t>
+          <t>2 substratenheter # grövre granlågor</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1303,12 +1228,7 @@
         <v>75235050</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595137.0800455887</v>
+        <v>595137</v>
       </c>
       <c r="R7" t="n">
-        <v>6846128.039465542</v>
+        <v>6846128</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,19 +1293,9 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-05-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75235052</v>
+        <v>75235051</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595310.1238658793</v>
+        <v>595208</v>
       </c>
       <c r="R8" t="n">
-        <v>6846359.919304456</v>
+        <v>6846284</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1498,21 +1403,11 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1524,15 +1419,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>naturskogsartad, ca 120-årig granskog i nordlut</t>
+          <t>äldre oskött granskog med björkinslag</t>
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>2 substratenheter # granlågor</t>
+          <t>1 substratenheter # grövre granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1550,15 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75235049</v>
+        <v>75235052</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595295.8848098154</v>
+        <v>595310</v>
       </c>
       <c r="R9" t="n">
-        <v>6846103.047355878</v>
+        <v>6846360</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1623,21 +1513,11 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1649,7 +1529,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>naturskogsartad luckig granskog</t>
+          <t>naturskogsartad, ca 120-årig granskog i nordlut</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1657,7 +1537,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>2 substratenheter # grövre granlågor</t>
+          <t>2 substratenheter # granlågor</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1675,37 +1555,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75235041</v>
+        <v>75235053</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1715,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595199.8876225286</v>
+        <v>595215</v>
       </c>
       <c r="R10" t="n">
-        <v>6846345.958840225</v>
+        <v>6846356</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1748,19 +1623,9 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-05-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,7 +1647,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # grövre granlåga</t>
+          <t>1 substratenheter # granlågor</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1797,6 +1662,446 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>75235040</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vallåsens nordostsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595306</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6846319</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>naturskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov låga av gammal gran</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>75235041</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vallåsens nordostsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595200</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6846346</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>naturskogsartad olikåldrig granskog i nordsluttning</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grövre granlåga</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>75235079</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vallåsens nordostsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595314</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6846318</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>5 substratenheter # gamla granar</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>75235076</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vallåsens nordostsida, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595227</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6846366</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>naturskogsartad granskog i nordsluttning</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>10 substratenheter # äldre granar</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
